--- a/content/zeiten.xlsx
+++ b/content/zeiten.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://basf-my.sharepoint.com/personal/losinsa_basfad_basf_net/Documents/Documents/ngba/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1636" documentId="11_AD4DB114E441178AC67DF49B9ED2F5E0693EDF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C512103B-8BAD-4313-BF52-8D4D1BE4B82C}"/>
+  <xr:revisionPtr revIDLastSave="1706" documentId="11_AD4DB114E441178AC67DF49B9ED2F5E0693EDF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4CB28BE-983D-4353-B31F-2E962F81B86A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="265">
   <si>
     <t>SpM27: Further investigation // New Process: Setting up Holger</t>
   </si>
@@ -819,6 +819,39 @@
   </si>
   <si>
     <t>enviDataReview // Draft Update Rules-Table  with File-SQL // Test: new TCG-DataType NCHAR</t>
+  </si>
+  <si>
+    <t>enviDataReview // Align Michael + Alice reg. RefSubIDMapping // Clear Rules from RefSubIDMapping</t>
+  </si>
+  <si>
+    <t>Stand-Up // Bug 1008434 // Align Patrizia reg. TCG-Import // Prese Del RefSubIDMapping from Rules</t>
+  </si>
+  <si>
+    <t>Stand-Up extended // Bug 1006911 // Prep Overview Mapper-Tabs for Klaus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bug 1009738 // Missing VAIUserDef-Texts // enviDataReview </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Alice reg. VAIUserDefTexts // Handover Klaus // </t>
+  </si>
+  <si>
+    <t>Stand-Up // Post-vacation activities // Meet Lydia // BUG 1012552</t>
+  </si>
+  <si>
+    <t>enviDataReview // Analyzing BUG 1012552</t>
+  </si>
+  <si>
+    <t>Stand-Up // Preparing and Executing SIT for BUG 1012552</t>
+  </si>
+  <si>
+    <t>Create Report for Alice (Bug 1012552) // enviDataReview // Klaus devOps credentails // Align Alice</t>
+  </si>
+  <si>
+    <t>Prep Meeting Welz with Alice // Meet Welz // Integrate Changes in Map-Tab for SpM07</t>
+  </si>
+  <si>
+    <t>Stand-Up // DevOps: Create new version with GIT // Meet Lydia // Align Klaus reg. GIT</t>
   </si>
 </sst>
 </file>
@@ -880,7 +913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -892,6 +925,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1173,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E78EEC-BD71-458B-9855-41A096F03DF9}">
   <sheetPr codeName="Tabelle2"/>
-  <dimension ref="A2:L320"/>
+  <dimension ref="A2:L337"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
@@ -4690,7 +4724,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>46211</v>
       </c>
@@ -4704,7 +4738,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>46212</v>
       </c>
@@ -4718,7 +4752,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>46213</v>
       </c>
@@ -4732,7 +4766,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>46216</v>
       </c>
@@ -4746,7 +4780,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>46217</v>
       </c>
@@ -4760,7 +4794,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>46218</v>
       </c>
@@ -4774,7 +4808,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>46219</v>
       </c>
@@ -4788,7 +4822,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>46220</v>
       </c>
@@ -4802,7 +4836,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>46223</v>
       </c>
@@ -4816,7 +4850,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>46224</v>
       </c>
@@ -4830,7 +4864,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>46225</v>
       </c>
@@ -4844,7 +4878,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>46226</v>
       </c>
@@ -4858,7 +4892,7 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>46227</v>
       </c>
@@ -4872,8 +4906,187 @@
         <v>202607</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="2"/>
+      <c r="J320" s="7"/>
+      <c r="K320" s="7"/>
+      <c r="L320" s="7"/>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A321" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C321" s="1">
+        <v>5</v>
+      </c>
+      <c r="D321" s="1">
+        <v>202608</v>
+      </c>
+      <c r="J321" s="7"/>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A322" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C322" s="1">
+        <v>5</v>
+      </c>
+      <c r="D322" s="1">
+        <v>202608</v>
+      </c>
+      <c r="J322" s="7"/>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A323" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C323" s="1">
+        <v>4</v>
+      </c>
+      <c r="D323" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A324" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C324" s="1">
+        <v>5</v>
+      </c>
+      <c r="D324" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A325" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C325" s="1">
+        <v>3</v>
+      </c>
+      <c r="D325" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A327" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C327" s="1">
+        <v>5</v>
+      </c>
+      <c r="D327" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A328" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C328" s="1">
+        <v>4</v>
+      </c>
+      <c r="D328" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A329" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C329" s="1">
+        <v>5</v>
+      </c>
+      <c r="D329" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A330" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C330" s="1">
+        <v>5</v>
+      </c>
+      <c r="D330" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A331" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C331" s="1">
+        <v>4</v>
+      </c>
+      <c r="D331" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A333" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C333" s="1">
+        <v>4</v>
+      </c>
+      <c r="D333" s="1">
+        <v>202608</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A334" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A335" s="2">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A336" s="2">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A337" s="2">
+        <v>46262</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
